--- a/per-stock/MRVL/financials.xlsx
+++ b/per-stock/MRVL/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>154876592128</v>
+        <v>271929278464</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156806430720</v>
+        <v>273128980480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57.43182</v>
+        <v>106.36301</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.611984</v>
+        <v>50.315666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18.899836</v>
+        <v>31.194925</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.51023996</v>
+        <v>0.5150299699999999</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.18655</v>
+        <v>0.14479999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.32584</v>
+        <v>0.28986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.19253999</v>
+        <v>0.16028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.221</v>
+        <v>0.276</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2638799872</v>
+        <v>3843599872</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4790300160</v>
+        <v>5277199872</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1442787456</v>
+        <v>1661500000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>176.89</v>
+        <v>310.58</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B42:E42)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B36:E36)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1738,13 +2218,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1753,6 +2233,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1763,25 +2244,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
@@ -1794,20 +2280,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-4280000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-3800000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-1361090.547982</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-1448138.639281</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2164891.153312</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>2625000</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1819,17 +2306,18 @@
         <v>0.4</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>0.14178</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.166453</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.176007</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1838,20 +2326,21 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>670700000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>758900000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>2592100000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>626600000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>588200000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>558200000</v>
-      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1860,20 +2349,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-10700000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-9500000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-8700000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>12300000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>12500000</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1882,20 +2372,21 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-10700000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-9500000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-8700000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>12300000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>12500000</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1904,20 +2395,21 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1926,20 +2418,21 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>320600000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>317000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>315900000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>327800000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>329900000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>325900000</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1948,20 +2441,21 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1157000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1070800000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>1004700000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>995500000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>942900000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>900000000</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1970,20 +2464,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>660000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>749400000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2582500000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>617900000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>600500000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>570700000</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1992,20 +2487,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>339400000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>432400000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>2266600000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>290100000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>270600000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>244800000</v>
-      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2014,20 +2510,21 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-256100000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-22800000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>1857600000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-56400000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-54700000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-35400000</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2036,20 +2533,21 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>256100000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>50800000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>51200000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>56400000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>54700000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>45000000</v>
-      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2057,15 +2555,16 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
         <v>28000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>1908800000</v>
       </c>
-      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n">
         <v>9600000</v>
       </c>
     </row>
@@ -2076,20 +2575,21 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>40920000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>401800000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>1909538909.452018</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>202051861.360719</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>167764891.153312</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>190325000</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2098,20 +2598,21 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2120,20 +2621,21 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>2067700000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>1804800000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>1707100000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>1707300000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>1637000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1594700000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2142,20 +2644,21 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>339400000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>404400000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>357800000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>290100000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>270600000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>235200000</v>
-      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2164,20 +2667,21 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>893300000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>856200000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>863700000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>870400000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>875600000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>879900000</v>
-      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2186,20 +2690,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>882000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>848000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>855800000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>862600000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>864800000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>865700000</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2208,20 +2713,21 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.46</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.22</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2230,20 +2736,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>2.22</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.23</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2252,20 +2759,21 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2274,20 +2782,21 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2296,20 +2805,21 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2318,20 +2828,21 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2340,20 +2851,21 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>200200000</v>
-      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2362,20 +2874,21 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>48800000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-14500000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>314100000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>38900000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-400000</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2384,20 +2897,21 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>83300000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>381600000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>2215400000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>233700000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>215900000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>199800000</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2406,20 +2920,21 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-10700000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-9500000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-8700000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>12300000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>12500000</v>
-      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2428,20 +2943,21 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-10700000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-9500000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-9600000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-8700000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>12300000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>12500000</v>
-      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2450,20 +2966,21 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>10700000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>9500000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>9600000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>8700000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-12300000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>-12500000</v>
-      </c>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2472,20 +2989,21 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-256100000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-22800000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1857600000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-56400000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-54700000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-35400000</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2494,20 +3012,21 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>256100000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>50800000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>51200000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>56400000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>54700000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>45000000</v>
-      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2515,15 +3034,16 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
         <v>28000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1908800000</v>
       </c>
-      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n">
         <v>9600000</v>
       </c>
     </row>
@@ -2534,20 +3054,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>350100000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>413900000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>367400000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>298800000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>258300000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>222700000</v>
-      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2556,20 +3077,21 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>910700000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>734000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>702400000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>711800000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>694100000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>694700000</v>
-      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2578,20 +3100,21 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>652300000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>536000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>512500000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>519000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>507700000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>499000000</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2600,20 +3123,21 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>258400000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>198000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>189900000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>192800000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>186400000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>195700000</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2622,20 +3146,21 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>1260800000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>1147900000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>1069800000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1010600000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>952400000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>917400000</v>
-      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2644,20 +3169,21 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>1157000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>1070800000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>1004700000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>995500000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>942900000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>900000000</v>
-      </c>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2666,20 +3192,21 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2417800000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2218700000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2074500000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>2006100000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>1895300000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>1817400000</v>
-      </c>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2688,27 +3215,28 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>2417800000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>2218700000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>2074500000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>2006100000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>1895300000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>1817400000</v>
-      </c>
+      <c r="G43" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4288,7 +4816,1863 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>875553173</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>847259927</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>848600000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>862100000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>862200000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>875553173</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>847259927</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>848600000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>862100000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>862200000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1117700000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1831800000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1754400000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3242800000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>3346700000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5277200000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4790300000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4777500000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4776300000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4512000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1490200000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1195200000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>699500000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-193700000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-576700000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>23177100000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>18779000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>18525500000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>17888900000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>17545300000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>5187200000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3240100000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2775800000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2113600000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>896200000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1490200000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1195200000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>699500000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-193700000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>-576700000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>315900000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>319700000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>308600000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>309100000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>279400000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>18215800000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>14308400000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>14056600000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>13421700000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>13312700000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>23177100000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>18279200000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>18026000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>17389600000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>16290100000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>18215800000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>14308400000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>14056600000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>13421700000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>13312700000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>18215800000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>14308400000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>14056600000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>13421700000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>13312700000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-300000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>1336500000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1355800000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1010500000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-840000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-983100000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>16877500000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>12950900000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>13044000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>14259400000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>14294200000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>8728700000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7976900000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>7522400000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>7164600000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>6711000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>6451900000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4756400000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4785700000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>4765300000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>3769600000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1013700000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>384500000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>409600000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>426300000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>452300000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>119800000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>117400000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>117800000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>79500000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>76500000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>95700000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>33900000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>33300000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>34200000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>95700000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>33900000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>33300000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>34200000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>5222700000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4234000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>4224400000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>4226200000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>3206600000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>261400000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>263200000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>255000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>258300000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>229200000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>4961300000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>3970800000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3969400000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3967900000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>2977400000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2276800000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>3220500000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2736700000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2399300000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2941400000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>63700000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>40100000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>32200000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>41300000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>63700000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>40100000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>32200000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>41300000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>31800000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>54500000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>556300000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>553100000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>550100000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1305400000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>54500000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>56500000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>50800000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>50200000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>499800000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>499500000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>499300000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1255200000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>129500000</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>499800000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>499500000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>499300000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1255200000</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>129500000</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>231500000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>309800000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>252400000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>210800000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>183700000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>19100000</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>11700000</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1927100000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>2314300000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1883300000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>1583200000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1389200000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1024800000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1012200000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>916000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>881300000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>748500000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>39900000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>45700000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>40100000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>48600000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>24900000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>902300000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1302100000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>967300000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>701900000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>640700000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>192600000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>228300000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>333600000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>91200000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>192600000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>228300000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>333600000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>91200000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>709700000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1073800000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>633700000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>610700000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>562700000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>26944500000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>22285300000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>21579000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>20586300000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>20023700000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>19480500000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>15824700000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>16066500000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>16073400000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>16186100000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>203300000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>153900000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>119600000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>106700000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>70900000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>835500000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>863000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>930700000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>800300000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>750300000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>319800000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>345900000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>403500000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>409900000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>405900000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>319800000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>345900000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>403500000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>409900000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>405900000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>140100000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>129600000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>128400000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>48600000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>140100000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>129600000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>128400000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>48600000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>16725600000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>13113200000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>13357100000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>13615400000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>13889400000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>2842100000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>2051000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>2294900000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2553200000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2827200000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>13883500000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>11062200000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>11062200000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>11062200000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>11062200000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1256200000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1219100000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1127200000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1068100000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1021000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-1467600000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-1407600000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-1357500000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-1308900000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-1272500000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2723800000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2626700000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>2484700000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>2377000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2293500000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>283700000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>284100000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>272400000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>273600000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>246300000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2095700000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>2003800000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1880300000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1781500000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1731500000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>344400000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>338800000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>332000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>321900000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>315700000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>7464000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>6460600000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>5512500000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>4512900000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>3837600000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>347800000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>247200000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>237200000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>189700000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>148100000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n">
+        <v>595500000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>588200000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1400900000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1388000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1014500000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1051600000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1071400000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>234400000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>282400000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>249000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>313000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>332400000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>1166500000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1105600000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>765500000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>738600000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>739000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1871700000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>2186600000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1546300000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1451700000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1144000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>1871700000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>2186600000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1546300000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1451700000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1144000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n">
+        <v>-4500000</v>
+      </c>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n">
+        <v>2191100000</v>
+      </c>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n">
+        <v>1031000000</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>3843600000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>2638800000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>2714500000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1224400000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>885900000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>3843600000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>2638800000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>2714500000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1224400000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>885900000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>72700000</v>
+      </c>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n">
+        <v>57200000</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n">
+        <v>2566100000</v>
+      </c>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n">
+        <v>891100000</v>
+      </c>
+      <c r="H77" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5520,13 +7904,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5536,6 +7920,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5546,30 +7931,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5582,21 +7972,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>482600000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>258300000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>507600000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>413000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>213000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>443300000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5605,21 +7996,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-200100000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-1300000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-200000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-340000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-200000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5628,21 +8020,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>-500000000</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>-757800000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-32800000</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-32800000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5651,1163 +8044,1291 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>998900000</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>998600000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Capital Expenditure</t>
+          <t>Issuance Of Capital Stock</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-115400000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>-74700000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>-48600000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-119900000</v>
-      </c>
+        <v>2000000000</v>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n">
-        <v>-70700000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>End Cash Position</t>
+          <t>Capital Expenditure</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2638800000</v>
+        <v>-156200000</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2714500000</v>
+        <v>-115400000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1224400000</v>
+        <v>-74700000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>885900000</v>
+        <v>-48600000</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>948300000</v>
+        <v>-119900000</v>
       </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Beginning Cash Position</t>
+          <t>End Cash Position</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>3843600000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2638800000</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>2714500000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>1224400000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>885900000</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>948300000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>868100000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Changes In Cash</t>
+          <t>Beginning Cash Position</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-75700000</v>
+        <v>2638800000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1490100000</v>
+        <v>2714500000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>338500000</v>
+        <v>1224400000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-62400000</v>
+        <v>885900000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>80200000</v>
+        <v>948300000</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Financing Cash Flow</t>
+          <t>Changes In Cash</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-327300000</v>
+        <v>1204800000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-1483400000</v>
+        <v>-75700000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-45900000</v>
+        <v>1490100000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-301200000</v>
+        <v>338500000</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-363500000</v>
+        <v>-62400000</v>
       </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Financing Activities</t>
+          <t>Financing Cash Flow</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>1987400000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-327300000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-1483400000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-45900000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-301200000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-363500000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Net Other Financing Charges</t>
+          <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-103600000</v>
+        <v>1987400000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-133000000</v>
+        <v>-327300000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-85500000</v>
+        <v>-1483400000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-77200000</v>
+        <v>-45900000</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-114000000</v>
+        <v>-301200000</v>
       </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Proceeds From Stock Option Exercised</t>
+          <t>Net Other Financing Charges</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>27200000</v>
+        <v>-261000000</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>400000</v>
+        <v>-103600000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>50500000</v>
+        <v>-133000000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>600000</v>
+        <v>-85500000</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>35200000</v>
+        <v>-77200000</v>
       </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cash Dividends Paid</t>
+          <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-50800000</v>
+        <v>3300000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>-50800000</v>
+        <v>27200000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-51700000</v>
+        <v>400000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-51800000</v>
+        <v>50500000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-51900000</v>
+        <v>600000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Common Stock Dividend Paid</t>
+          <t>Cash Dividends Paid</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-50800000</v>
+        <v>-53800000</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>-50800000</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>-50800000</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>-51700000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-51800000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-51900000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
+          <t>Common Stock Dividend Paid</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-200100000</v>
+        <v>-53800000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1300000000</v>
+        <v>-50800000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-200000000</v>
+        <v>-50800000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-340000000</v>
+        <v>-51700000</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-200000000</v>
+        <v>-51800000</v>
       </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Common Stock Payments</t>
+          <t>Net Preferred Stock Issuance</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-200100000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>-1300000000</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>-200000000</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-340000000</v>
-      </c>
+        <v>2000000000</v>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n">
-        <v>-200000000</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
+          <t>Preferred Stock Issuance</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>240800000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>167200000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>-32800000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Net Common Stock Issuance</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>-200000000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>-200100000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>240800000</v>
+        <v>-1300000000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>167200000</v>
+        <v>-200000000</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-32800000</v>
+        <v>-340000000</v>
       </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Common Stock Payments</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0</v>
+        <v>-200000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>-200100000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-757800000</v>
+        <v>-1300000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-32800000</v>
+        <v>-200000000</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-32800000</v>
+        <v>-340000000</v>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
+          <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>498900000</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>998600000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>200000000</v>
+        <v>240800000</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>167200000</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-122100000</v>
+        <v>498900000</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2391200000</v>
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-77200000</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>-94100000</v>
+        <v>240800000</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-70300000</v>
+        <v>167200000</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-122100000</v>
+        <v>-500000000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2391200000</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-77200000</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-94100000</v>
+        <v>-757800000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-70300000</v>
+        <v>-32800000</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-6700000</v>
+        <v>998900000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-12800000</v>
+        <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-30000000</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-100000</v>
+        <v>998600000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>400000</v>
+        <v>200000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
+          <t>Investing Cash Flow</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+        <v>-1421400000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-122100000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2391200000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-77200000</v>
+      </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-94100000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sale Of Business</t>
+          <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
+        <v>-1421400000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-122100000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2391200000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-77200000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-94100000</v>
+      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+        <v>5700000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-6700000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-12800000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-30000000</v>
+      </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-100000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Net Intangibles Purchase And Sale</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-1100000</v>
+        <v>-1270900000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-1200000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>-1100000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-1100000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="G28" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Purchase Of Intangibles</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>-1100000</v>
-      </c>
+          <t>Sale Of Business</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n">
-        <v>-1200000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>-1100000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-1100000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>-800000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Purchase Of Business</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-114300000</v>
+        <v>-1270900000</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-73400000</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>-46100000</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-92900000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>-69900000</v>
-      </c>
-      <c r="G30" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sale Of PPE</t>
+          <t>Net Intangibles Purchase And Sale</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-500000</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>100000</v>
+        <v>-1100000</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1400000</v>
+        <v>-1200000</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>25900000</v>
-      </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n">
-        <v>100000</v>
-      </c>
+        <v>-1100000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-1100000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
+          <t>Purchase Of Intangibles</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-114300000</v>
+        <v>-500000</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-73500000</v>
+        <v>-1100000</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-47500000</v>
+        <v>-1200000</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-118800000</v>
+        <v>-1100000</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-69900000</v>
+        <v>-1100000</v>
       </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>373700000</v>
+        <v>-155700000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>582300000</v>
+        <v>-114300000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>461600000</v>
+        <v>-73400000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>332900000</v>
+        <v>-46100000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>514000000</v>
+        <v>-92900000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Sale Of PPE</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>373700000</v>
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>582300000</v>
+        <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>461600000</v>
+        <v>100000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>332900000</v>
+        <v>1400000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>514000000</v>
+        <v>25900000</v>
       </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Purchase Of PPE</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-551200000</v>
+        <v>-155700000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>32100000</v>
+        <v>-114300000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-246400000</v>
+        <v>-73500000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-342800000</v>
+        <v>-47500000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-182500000</v>
+        <v>-118800000</v>
       </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Change In Payables And Accrued Expense</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>418400000</v>
+        <v>638800000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>281700000</v>
+        <v>373700000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>163400000</v>
+        <v>582300000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-181400000</v>
+        <v>461600000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>190600000</v>
+        <v>332900000</v>
       </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Change In Accrued Expense</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>40000000</v>
+        <v>638800000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>292700000</v>
+        <v>373700000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>194100000</v>
+        <v>582300000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-144000000</v>
+        <v>461600000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>118900000</v>
+        <v>332900000</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>378400000</v>
+        <v>-211600000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>-11000000</v>
+        <v>-551200000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>-30700000</v>
+        <v>32100000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-37400000</v>
+        <v>-246400000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>71700000</v>
+        <v>-342800000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Change In Account Payable</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>378400000</v>
+        <v>-486600000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>-11000000</v>
+        <v>418400000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-30700000</v>
+        <v>281700000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-37400000</v>
+        <v>163400000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>71700000</v>
+        <v>-181400000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Change In Prepaid Assets</t>
+          <t>Change In Accrued Expense</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>41100000</v>
+        <v>-130700000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-190100000</v>
+        <v>40000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-117500000</v>
+        <v>292700000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>24100000</v>
+        <v>194100000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-172800000</v>
+        <v>-144000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Change In Inventory</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>-370500000</v>
+        <v>-355900000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>35200000</v>
+        <v>378400000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>15400000</v>
+        <v>-11000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-69900000</v>
+        <v>-30700000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-169800000</v>
+        <v>-37400000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>-640200000</v>
+        <v>-355900000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>-94700000</v>
+        <v>378400000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>-307700000</v>
+        <v>-11000000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>-115600000</v>
+        <v>-30700000</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>-30500000</v>
+        <v>-37400000</v>
       </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Changes In Account Receivables</t>
+          <t>Change In Prepaid Assets</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>-640200000</v>
+        <v>-28500000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>-94700000</v>
+        <v>41100000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-307700000</v>
+        <v>-190100000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-115600000</v>
+        <v>-117500000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-30500000</v>
+        <v>24100000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>24400000</v>
+        <v>-11400000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>4300000</v>
+        <v>-370500000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>36700000</v>
+        <v>35200000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>30100000</v>
+        <v>15400000</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>23800000</v>
+        <v>-69900000</v>
       </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>143000000</v>
+        <v>314900000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>152100000</v>
+        <v>-640200000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>153600000</v>
+        <v>-94700000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>142100000</v>
+        <v>-307700000</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>147600000</v>
+        <v>-115600000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Asset Impairment Charge</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+          <t>Changes In Account Receivables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>314900000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>-640200000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>-94700000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-307700000</v>
+      </c>
       <c r="F46" s="3" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>521800000</v>
-      </c>
+        <v>-115600000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deferred Tax</t>
+          <t>Other Non Cash Items</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>44400000</v>
+        <v>355000000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>7000000</v>
+        <v>24400000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>-4900000</v>
+        <v>4300000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>-4300000</v>
+        <v>36700000</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-5700000</v>
+        <v>30100000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Deferred Income Tax</t>
+          <t>Stock Based Compensation</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>44400000</v>
+        <v>207600000</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7000000</v>
+        <v>143000000</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>-4900000</v>
+        <v>152100000</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-4300000</v>
+        <v>153600000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>-5700000</v>
+        <v>142100000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>317000000</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>315900000</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>327800000</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>329900000</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>325900000</v>
-      </c>
-      <c r="G49" s="3" t="n"/>
+          <t>Asset Impairment Charge</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>521800000</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Deferred Tax</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>317000000</v>
+        <v>13800000</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>315900000</v>
+        <v>44400000</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>327800000</v>
+        <v>7000000</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>329900000</v>
+        <v>-4900000</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>325900000</v>
+        <v>-4300000</v>
       </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Amortization Cash Flow</t>
+          <t>Deferred Income Tax</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>223600000</v>
+        <v>13800000</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>229000000</v>
+        <v>44400000</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>243700000</v>
+        <v>7000000</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>245700000</v>
+        <v>-4900000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>247100000</v>
+        <v>-4300000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles</t>
+          <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>223600000</v>
+        <v>320600000</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>229000000</v>
+        <v>317000000</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>243700000</v>
+        <v>315900000</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>245700000</v>
+        <v>327800000</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>247100000</v>
+        <v>329900000</v>
       </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Depreciation And Amortization</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>93400000</v>
+        <v>320600000</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>86900000</v>
+        <v>317000000</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>84100000</v>
+        <v>315900000</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>84200000</v>
+        <v>327800000</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>78800000</v>
+        <v>329900000</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Amortization Cash Flow</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
+        <v>225200000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>223600000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>243700000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>245700000</v>
+      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gain Loss On Sale Of Business</t>
+          <t>Amortization Of Intangibles</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
+        <v>225200000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>223600000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>243700000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>245700000</v>
+      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>95400000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>93400000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>86900000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>84100000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>84200000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>-81100000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gain Loss On Investment Securities</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>-81100000</v>
+      </c>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gain Loss On Sale Of Business</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B60" s="3" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>396100000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>1901300000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>194800000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>177900000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>200200000</v>
-      </c>
-      <c r="G56" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
